--- a/Bases_de_Dados/FootyStats/Spain Segunda División_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Spain Segunda División_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP302"/>
+  <dimension ref="A1:BP303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.14</v>
@@ -5274,7 +5274,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.93</v>
@@ -9852,7 +9852,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR43" t="n">
         <v>3.16</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.77</v>
@@ -14866,7 +14866,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR66" t="n">
         <v>1.39</v>
@@ -19005,7 +19005,7 @@
         <v>1</v>
       </c>
       <c r="AP85" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.23</v>
@@ -21406,7 +21406,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR96" t="n">
         <v>1.88</v>
@@ -23583,7 +23583,7 @@
         <v>1.2</v>
       </c>
       <c r="AP106" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ106" t="n">
         <v>1.21</v>
@@ -25984,7 +25984,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR117" t="n">
         <v>1.16</v>
@@ -28815,7 +28815,7 @@
         <v>0.6</v>
       </c>
       <c r="AP130" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.14</v>
@@ -30998,7 +30998,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR140" t="n">
         <v>1.41</v>
@@ -32085,7 +32085,7 @@
         <v>0</v>
       </c>
       <c r="AP145" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.79</v>
@@ -36012,7 +36012,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR163" t="n">
         <v>1.22</v>
@@ -39061,7 +39061,7 @@
         <v>1.86</v>
       </c>
       <c r="AP177" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.46</v>
@@ -39936,7 +39936,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR181" t="n">
         <v>1.34</v>
@@ -43857,7 +43857,7 @@
         <v>1</v>
       </c>
       <c r="AP199" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ199" t="n">
         <v>0.86</v>
@@ -44514,7 +44514,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR202" t="n">
         <v>1.37</v>
@@ -47127,7 +47127,7 @@
         <v>0.78</v>
       </c>
       <c r="AP214" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ214" t="n">
         <v>0.57</v>
@@ -47348,7 +47348,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ215" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR215" t="n">
         <v>1.96</v>
@@ -51269,7 +51269,7 @@
         <v>1.55</v>
       </c>
       <c r="AP233" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ233" t="n">
         <v>1.21</v>
@@ -55632,7 +55632,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ253" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR253" t="n">
         <v>1.5</v>
@@ -57591,7 +57591,7 @@
         <v>1.25</v>
       </c>
       <c r="AP262" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ262" t="n">
         <v>1.07</v>
@@ -58030,7 +58030,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ264" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR264" t="n">
         <v>1.53</v>
@@ -61954,7 +61954,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ282" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR282" t="n">
         <v>1.8</v>
@@ -62605,7 +62605,7 @@
         <v>1.85</v>
       </c>
       <c r="AP285" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ285" t="n">
         <v>1.71</v>
@@ -66390,6 +66390,224 @@
       </c>
       <c r="BP302" t="n">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="n">
+        <v>8234975</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="n">
+        <v>46081.70833333334</v>
+      </c>
+      <c r="F303" t="n">
+        <v>28</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>CD Castellón</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="I303" t="n">
+        <v>0</v>
+      </c>
+      <c r="J303" t="n">
+        <v>3</v>
+      </c>
+      <c r="K303" t="n">
+        <v>3</v>
+      </c>
+      <c r="L303" t="n">
+        <v>1</v>
+      </c>
+      <c r="M303" t="n">
+        <v>3</v>
+      </c>
+      <c r="N303" t="n">
+        <v>4</v>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>['19', '34', '42']</t>
+        </is>
+      </c>
+      <c r="Q303" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R303" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S303" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T303" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U303" t="n">
+        <v>3</v>
+      </c>
+      <c r="V303" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W303" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X303" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="Y303" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z303" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA303" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB303" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC303" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD303" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE303" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF303" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG303" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH303" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI303" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ303" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AK303" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM303" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AN303" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO303" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AP303" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ303" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR303" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS303" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT303" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AU303" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV303" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW303" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX303" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY303" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ303" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA303" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB303" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC303" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD303" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BE303" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF303" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG303" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH303" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI303" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ303" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BK303" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BL303" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM303" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BN303" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO303" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BP303" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Spain Segunda División_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Spain Segunda División_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP303"/>
+  <dimension ref="A1:BP309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.93</v>
@@ -2440,7 +2440,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.43</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ13" t="n">
         <v>1</v>
@@ -3748,7 +3748,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ16" t="n">
         <v>0.57</v>
@@ -4402,7 +4402,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.43</v>
@@ -5489,10 +5489,10 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR23" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
         <v>3</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.43</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.21</v>
@@ -6146,7 +6146,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR26" t="n">
         <v>1.17</v>
@@ -7890,7 +7890,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR34" t="n">
         <v>1.16</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.43</v>
@@ -9413,10 +9413,10 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR41" t="n">
         <v>0.74</v>
@@ -9634,7 +9634,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR42" t="n">
         <v>1.91</v>
@@ -10067,10 +10067,10 @@
         <v>1</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR44" t="n">
         <v>1.26</v>
@@ -10285,10 +10285,10 @@
         <v>2</v>
       </c>
       <c r="AP45" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR45" t="n">
         <v>1.84</v>
@@ -10721,10 +10721,10 @@
         <v>2</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR47" t="n">
         <v>0.71</v>
@@ -12029,7 +12029,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.43</v>
@@ -12250,7 +12250,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR54" t="n">
         <v>1.6</v>
@@ -12468,7 +12468,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR55" t="n">
         <v>1.49</v>
@@ -13119,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ58" t="n">
         <v>1.43</v>
@@ -13340,7 +13340,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR59" t="n">
         <v>1.57</v>
@@ -14427,7 +14427,7 @@
         <v>0</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.79</v>
@@ -14648,7 +14648,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR65" t="n">
         <v>1.48</v>
@@ -14863,7 +14863,7 @@
         <v>3</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.71</v>
@@ -15299,7 +15299,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ68" t="n">
         <v>0.93</v>
@@ -15520,7 +15520,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR69" t="n">
         <v>1.85</v>
@@ -15735,10 +15735,10 @@
         <v>2.33</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR70" t="n">
         <v>1.76</v>
@@ -16171,7 +16171,7 @@
         <v>0.33</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.43</v>
@@ -16610,7 +16610,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR74" t="n">
         <v>1.49</v>
@@ -16825,7 +16825,7 @@
         <v>0.67</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.21</v>
@@ -18136,7 +18136,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR81" t="n">
         <v>1.74</v>
@@ -19662,7 +19662,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR88" t="n">
         <v>1.43</v>
@@ -19877,7 +19877,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.21</v>
@@ -20098,7 +20098,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR90" t="n">
         <v>1.45</v>
@@ -20313,10 +20313,10 @@
         <v>2</v>
       </c>
       <c r="AP91" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR91" t="n">
         <v>1.12</v>
@@ -20749,10 +20749,10 @@
         <v>1.75</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR93" t="n">
         <v>1.14</v>
@@ -20970,7 +20970,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR94" t="n">
         <v>1.68</v>
@@ -21185,7 +21185,7 @@
         <v>1.5</v>
       </c>
       <c r="AP95" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.43</v>
@@ -21403,7 +21403,7 @@
         <v>2.33</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ96" t="n">
         <v>1.71</v>
@@ -22060,7 +22060,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR99" t="n">
         <v>1.59</v>
@@ -22275,7 +22275,7 @@
         <v>1.5</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ100" t="n">
         <v>1.21</v>
@@ -23804,7 +23804,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR107" t="n">
         <v>1.89</v>
@@ -24019,7 +24019,7 @@
         <v>1.6</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.43</v>
@@ -24676,7 +24676,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR111" t="n">
         <v>1.32</v>
@@ -24891,10 +24891,10 @@
         <v>0.6</v>
       </c>
       <c r="AP112" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR112" t="n">
         <v>0.99</v>
@@ -25327,10 +25327,10 @@
         <v>1.8</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR114" t="n">
         <v>1.72</v>
@@ -25548,7 +25548,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR115" t="n">
         <v>1.36</v>
@@ -25981,7 +25981,7 @@
         <v>1.75</v>
       </c>
       <c r="AP117" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.71</v>
@@ -26202,7 +26202,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR118" t="n">
         <v>1.58</v>
@@ -26635,7 +26635,7 @@
         <v>0.8</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ120" t="n">
         <v>0.93</v>
@@ -27289,7 +27289,7 @@
         <v>1.33</v>
       </c>
       <c r="AP123" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.86</v>
@@ -28164,7 +28164,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR127" t="n">
         <v>1.55</v>
@@ -28379,10 +28379,10 @@
         <v>1.8</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR128" t="n">
         <v>1.56</v>
@@ -28597,10 +28597,10 @@
         <v>1</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR129" t="n">
         <v>1.71</v>
@@ -29036,7 +29036,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR131" t="n">
         <v>1.13</v>
@@ -29469,7 +29469,7 @@
         <v>0.6</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ133" t="n">
         <v>0.57</v>
@@ -29687,7 +29687,7 @@
         <v>1.2</v>
       </c>
       <c r="AP134" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ134" t="n">
         <v>1.23</v>
@@ -29905,10 +29905,10 @@
         <v>1.67</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR135" t="n">
         <v>1.14</v>
@@ -30123,7 +30123,7 @@
         <v>1.5</v>
       </c>
       <c r="AP136" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ136" t="n">
         <v>1.21</v>
@@ -30344,7 +30344,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR137" t="n">
         <v>1.31</v>
@@ -31870,7 +31870,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR144" t="n">
         <v>1.93</v>
@@ -32306,7 +32306,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR146" t="n">
         <v>1.67</v>
@@ -32742,7 +32742,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR148" t="n">
         <v>1.46</v>
@@ -32957,7 +32957,7 @@
         <v>0.17</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.38</v>
@@ -33178,7 +33178,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR150" t="n">
         <v>2.17</v>
@@ -33393,7 +33393,7 @@
         <v>1.67</v>
       </c>
       <c r="AP151" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.43</v>
@@ -33611,10 +33611,10 @@
         <v>1.57</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR152" t="n">
         <v>1.68</v>
@@ -34047,7 +34047,7 @@
         <v>0.5</v>
       </c>
       <c r="AP154" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ154" t="n">
         <v>1.14</v>
@@ -34919,7 +34919,7 @@
         <v>0.57</v>
       </c>
       <c r="AP158" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ158" t="n">
         <v>0.93</v>
@@ -35358,7 +35358,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR160" t="n">
         <v>1.4</v>
@@ -36445,7 +36445,7 @@
         <v>1.5</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.14</v>
@@ -36881,10 +36881,10 @@
         <v>1</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR167" t="n">
         <v>1.46</v>
@@ -37317,7 +37317,7 @@
         <v>1</v>
       </c>
       <c r="AP169" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ169" t="n">
         <v>1</v>
@@ -37538,7 +37538,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR170" t="n">
         <v>1.69</v>
@@ -38192,7 +38192,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR173" t="n">
         <v>1.11</v>
@@ -38625,10 +38625,10 @@
         <v>1</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR175" t="n">
         <v>1.78</v>
@@ -38843,7 +38843,7 @@
         <v>0</v>
       </c>
       <c r="AP176" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ176" t="n">
         <v>0.79</v>
@@ -39064,7 +39064,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR177" t="n">
         <v>1.94</v>
@@ -39715,7 +39715,7 @@
         <v>0.86</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ180" t="n">
         <v>1.23</v>
@@ -40369,7 +40369,7 @@
         <v>1.5</v>
       </c>
       <c r="AP183" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.21</v>
@@ -40808,7 +40808,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR185" t="n">
         <v>1.52</v>
@@ -41677,7 +41677,7 @@
         <v>0.5</v>
       </c>
       <c r="AP189" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ189" t="n">
         <v>0.57</v>
@@ -41895,7 +41895,7 @@
         <v>0.25</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ190" t="n">
         <v>0.38</v>
@@ -42113,7 +42113,7 @@
         <v>1.25</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ191" t="n">
         <v>1</v>
@@ -42334,7 +42334,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR192" t="n">
         <v>1.97</v>
@@ -42552,7 +42552,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR193" t="n">
         <v>1.76</v>
@@ -42770,7 +42770,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR194" t="n">
         <v>1.29</v>
@@ -43642,7 +43642,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR198" t="n">
         <v>1.45</v>
@@ -44075,7 +44075,7 @@
         <v>1.5</v>
       </c>
       <c r="AP200" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ200" t="n">
         <v>1.14</v>
@@ -44296,7 +44296,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR201" t="n">
         <v>1.57</v>
@@ -45383,10 +45383,10 @@
         <v>0.78</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ206" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR206" t="n">
         <v>1.14</v>
@@ -45601,7 +45601,7 @@
         <v>1.22</v>
       </c>
       <c r="AP207" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ207" t="n">
         <v>1.43</v>
@@ -46473,7 +46473,7 @@
         <v>0.9</v>
       </c>
       <c r="AP211" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ211" t="n">
         <v>0.86</v>
@@ -46691,7 +46691,7 @@
         <v>0.33</v>
       </c>
       <c r="AP212" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ212" t="n">
         <v>0.79</v>
@@ -47563,7 +47563,7 @@
         <v>1.78</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ216" t="n">
         <v>1.43</v>
@@ -47781,7 +47781,7 @@
         <v>0.78</v>
       </c>
       <c r="AP217" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ217" t="n">
         <v>1.14</v>
@@ -48002,7 +48002,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ218" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR218" t="n">
         <v>1.47</v>
@@ -48220,7 +48220,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ219" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR219" t="n">
         <v>1.3</v>
@@ -48438,7 +48438,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR220" t="n">
         <v>1.61</v>
@@ -48656,7 +48656,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ221" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR221" t="n">
         <v>1.46</v>
@@ -49089,7 +49089,7 @@
         <v>1.5</v>
       </c>
       <c r="AP223" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ223" t="n">
         <v>1.43</v>
@@ -49307,7 +49307,7 @@
         <v>1.3</v>
       </c>
       <c r="AP224" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ224" t="n">
         <v>1.21</v>
@@ -49964,7 +49964,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ227" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR227" t="n">
         <v>1.34</v>
@@ -50836,7 +50836,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ231" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR231" t="n">
         <v>1.72</v>
@@ -51272,7 +51272,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ233" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR233" t="n">
         <v>1.87</v>
@@ -51705,7 +51705,7 @@
         <v>1.2</v>
       </c>
       <c r="AP235" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ235" t="n">
         <v>1.23</v>
@@ -52144,7 +52144,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ237" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR237" t="n">
         <v>2.05</v>
@@ -52359,10 +52359,10 @@
         <v>1.09</v>
       </c>
       <c r="AP238" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ238" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR238" t="n">
         <v>1.33</v>
@@ -52580,7 +52580,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ239" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR239" t="n">
         <v>1.84</v>
@@ -53016,7 +53016,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ241" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR241" t="n">
         <v>1.6</v>
@@ -53231,7 +53231,7 @@
         <v>1</v>
       </c>
       <c r="AP242" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ242" t="n">
         <v>1.14</v>
@@ -54321,7 +54321,7 @@
         <v>0.82</v>
       </c>
       <c r="AP247" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ247" t="n">
         <v>0.86</v>
@@ -55193,7 +55193,7 @@
         <v>1.45</v>
       </c>
       <c r="AP251" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ251" t="n">
         <v>1.43</v>
@@ -56065,10 +56065,10 @@
         <v>1.55</v>
       </c>
       <c r="AP255" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ255" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR255" t="n">
         <v>1.14</v>
@@ -56504,7 +56504,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ257" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR257" t="n">
         <v>1.25</v>
@@ -56719,10 +56719,10 @@
         <v>1.75</v>
       </c>
       <c r="AP258" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ258" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR258" t="n">
         <v>1.3</v>
@@ -56937,7 +56937,7 @@
         <v>1.36</v>
       </c>
       <c r="AP259" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ259" t="n">
         <v>1.14</v>
@@ -57158,7 +57158,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ260" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR260" t="n">
         <v>1.97</v>
@@ -57373,7 +57373,7 @@
         <v>1.36</v>
       </c>
       <c r="AP261" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ261" t="n">
         <v>1.23</v>
@@ -57594,7 +57594,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ262" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR262" t="n">
         <v>1.85</v>
@@ -57812,7 +57812,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ263" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR263" t="n">
         <v>1.37</v>
@@ -58245,7 +58245,7 @@
         <v>1.18</v>
       </c>
       <c r="AP265" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ265" t="n">
         <v>1.14</v>
@@ -59989,7 +59989,7 @@
         <v>0.67</v>
       </c>
       <c r="AP273" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ273" t="n">
         <v>0.57</v>
@@ -60646,7 +60646,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ276" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR276" t="n">
         <v>1.97</v>
@@ -60861,10 +60861,10 @@
         <v>1.31</v>
       </c>
       <c r="AP277" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ277" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR277" t="n">
         <v>1.83</v>
@@ -61082,7 +61082,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ278" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR278" t="n">
         <v>1.23</v>
@@ -61297,7 +61297,7 @@
         <v>1</v>
       </c>
       <c r="AP279" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ279" t="n">
         <v>0.93</v>
@@ -61733,10 +61733,10 @@
         <v>1.5</v>
       </c>
       <c r="AP281" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ281" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR281" t="n">
         <v>1.4</v>
@@ -61951,7 +61951,7 @@
         <v>1.75</v>
       </c>
       <c r="AP282" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ282" t="n">
         <v>1.71</v>
@@ -62172,7 +62172,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ283" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR283" t="n">
         <v>1.38</v>
@@ -62608,7 +62608,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ285" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR285" t="n">
         <v>1.86</v>
@@ -62823,7 +62823,7 @@
         <v>1.08</v>
       </c>
       <c r="AP286" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ286" t="n">
         <v>1.14</v>
@@ -64349,7 +64349,7 @@
         <v>1.15</v>
       </c>
       <c r="AP293" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ293" t="n">
         <v>1.14</v>
@@ -66608,6 +66608,1314 @@
       </c>
       <c r="BP303" t="n">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="n">
+        <v>8235319</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="n">
+        <v>46082.41666666666</v>
+      </c>
+      <c r="F304" t="n">
+        <v>28</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Real Sociedad II</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Deportivo La Coruña</t>
+        </is>
+      </c>
+      <c r="I304" t="n">
+        <v>1</v>
+      </c>
+      <c r="J304" t="n">
+        <v>1</v>
+      </c>
+      <c r="K304" t="n">
+        <v>2</v>
+      </c>
+      <c r="L304" t="n">
+        <v>2</v>
+      </c>
+      <c r="M304" t="n">
+        <v>3</v>
+      </c>
+      <c r="N304" t="n">
+        <v>5</v>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>['23', '59']</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>['2', '83', '90+4']</t>
+        </is>
+      </c>
+      <c r="Q304" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R304" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S304" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T304" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U304" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V304" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="W304" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X304" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y304" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z304" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AA304" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AB304" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC304" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD304" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE304" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF304" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AG304" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH304" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI304" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ304" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AK304" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM304" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN304" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO304" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AP304" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ304" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR304" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AS304" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT304" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU304" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV304" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW304" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX304" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY304" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ304" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA304" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB304" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC304" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD304" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BE304" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF304" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BG304" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH304" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BI304" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ304" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BK304" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BL304" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM304" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BN304" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO304" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP304" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="n">
+        <v>8235074</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="n">
+        <v>46082.51041666666</v>
+      </c>
+      <c r="F305" t="n">
+        <v>28</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Mirandés</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Ceuta</t>
+        </is>
+      </c>
+      <c r="I305" t="n">
+        <v>0</v>
+      </c>
+      <c r="J305" t="n">
+        <v>1</v>
+      </c>
+      <c r="K305" t="n">
+        <v>1</v>
+      </c>
+      <c r="L305" t="n">
+        <v>0</v>
+      </c>
+      <c r="M305" t="n">
+        <v>1</v>
+      </c>
+      <c r="N305" t="n">
+        <v>1</v>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="Q305" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R305" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S305" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="T305" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U305" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V305" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W305" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X305" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Y305" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z305" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA305" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB305" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC305" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD305" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE305" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF305" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG305" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH305" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI305" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ305" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AK305" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM305" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AN305" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AO305" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AP305" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AQ305" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR305" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS305" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT305" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AU305" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV305" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW305" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX305" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY305" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ305" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA305" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB305" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC305" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD305" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BE305" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF305" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG305" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH305" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BI305" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BJ305" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BK305" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BL305" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BM305" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BN305" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BO305" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="BP305" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="n">
+        <v>8235208</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="n">
+        <v>46082.60416666666</v>
+      </c>
+      <c r="F306" t="n">
+        <v>28</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Cultural y Deportiva Leonesa</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>UD Las Palmas</t>
+        </is>
+      </c>
+      <c r="I306" t="n">
+        <v>0</v>
+      </c>
+      <c r="J306" t="n">
+        <v>0</v>
+      </c>
+      <c r="K306" t="n">
+        <v>0</v>
+      </c>
+      <c r="L306" t="n">
+        <v>0</v>
+      </c>
+      <c r="M306" t="n">
+        <v>3</v>
+      </c>
+      <c r="N306" t="n">
+        <v>3</v>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>['48', '57', '90+1']</t>
+        </is>
+      </c>
+      <c r="Q306" t="n">
+        <v>4</v>
+      </c>
+      <c r="R306" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S306" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T306" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U306" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V306" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W306" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X306" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y306" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z306" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AA306" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AB306" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC306" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD306" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE306" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF306" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AG306" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH306" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI306" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ306" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK306" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM306" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN306" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AO306" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP306" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AQ306" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR306" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AS306" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT306" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AU306" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV306" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW306" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX306" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY306" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ306" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA306" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB306" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC306" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD306" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BE306" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF306" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BG306" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BH306" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BI306" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BJ306" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BK306" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BL306" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BM306" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BN306" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BO306" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP306" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="n">
+        <v>8235073</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="n">
+        <v>46082.70833333334</v>
+      </c>
+      <c r="F307" t="n">
+        <v>28</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>SD Eibar</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="I307" t="n">
+        <v>2</v>
+      </c>
+      <c r="J307" t="n">
+        <v>0</v>
+      </c>
+      <c r="K307" t="n">
+        <v>2</v>
+      </c>
+      <c r="L307" t="n">
+        <v>3</v>
+      </c>
+      <c r="M307" t="n">
+        <v>1</v>
+      </c>
+      <c r="N307" t="n">
+        <v>4</v>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>['34', '42', '83']</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="Q307" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R307" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S307" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T307" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U307" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V307" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W307" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X307" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y307" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z307" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA307" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AB307" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AC307" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD307" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AE307" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF307" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG307" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH307" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI307" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ307" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AK307" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM307" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN307" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO307" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AP307" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ307" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR307" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS307" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AT307" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AU307" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV307" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW307" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX307" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY307" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ307" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA307" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB307" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC307" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD307" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BE307" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF307" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG307" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH307" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI307" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ307" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BK307" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BL307" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BM307" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN307" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO307" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP307" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="n">
+        <v>8235210</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="n">
+        <v>46083.66666666666</v>
+      </c>
+      <c r="F308" t="n">
+        <v>28</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Sporting Gijón</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Leganés</t>
+        </is>
+      </c>
+      <c r="I308" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" t="n">
+        <v>0</v>
+      </c>
+      <c r="K308" t="n">
+        <v>0</v>
+      </c>
+      <c r="L308" t="n">
+        <v>0</v>
+      </c>
+      <c r="M308" t="n">
+        <v>0</v>
+      </c>
+      <c r="N308" t="n">
+        <v>0</v>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q308" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R308" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S308" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T308" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U308" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V308" t="n">
+        <v>3</v>
+      </c>
+      <c r="W308" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X308" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y308" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z308" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA308" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AB308" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AC308" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD308" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AE308" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF308" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG308" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH308" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI308" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ308" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK308" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL308" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM308" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN308" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO308" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AP308" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ308" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR308" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS308" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT308" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AU308" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV308" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW308" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX308" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY308" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ308" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA308" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB308" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC308" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD308" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE308" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF308" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG308" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH308" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BI308" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ308" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BK308" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BL308" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BM308" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BN308" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO308" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP308" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" t="n">
+        <v>8235143</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="n">
+        <v>46083.6875</v>
+      </c>
+      <c r="F309" t="n">
+        <v>28</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>FC Andorra</t>
+        </is>
+      </c>
+      <c r="I309" t="n">
+        <v>0</v>
+      </c>
+      <c r="J309" t="n">
+        <v>3</v>
+      </c>
+      <c r="K309" t="n">
+        <v>3</v>
+      </c>
+      <c r="L309" t="n">
+        <v>1</v>
+      </c>
+      <c r="M309" t="n">
+        <v>4</v>
+      </c>
+      <c r="N309" t="n">
+        <v>5</v>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>['9', '15', '30', '74']</t>
+        </is>
+      </c>
+      <c r="Q309" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R309" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S309" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="T309" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U309" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V309" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W309" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X309" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y309" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z309" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA309" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB309" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC309" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD309" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AE309" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF309" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG309" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH309" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI309" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ309" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK309" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM309" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AN309" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO309" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AP309" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ309" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR309" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS309" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT309" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AU309" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV309" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW309" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX309" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY309" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ309" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA309" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB309" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC309" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD309" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE309" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF309" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG309" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH309" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BI309" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ309" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK309" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BL309" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BM309" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BN309" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO309" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP309" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Spain Segunda División_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Spain Segunda División_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP309"/>
+  <dimension ref="A1:BP312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.86</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.2</v>
@@ -3094,7 +3094,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
         <v>3</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.43</v>
@@ -6582,7 +6582,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR28" t="n">
         <v>1.46</v>
@@ -7015,10 +7015,10 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR30" t="n">
         <v>2.37</v>
@@ -7669,7 +7669,7 @@
         <v>1</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ33" t="n">
         <v>0.38</v>
@@ -8326,7 +8326,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR36" t="n">
         <v>1.51</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.07</v>
@@ -10939,7 +10939,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.38</v>
@@ -11157,7 +11157,7 @@
         <v>3</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.14</v>
@@ -12686,7 +12686,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR56" t="n">
         <v>1.3</v>
@@ -13122,7 +13122,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR58" t="n">
         <v>1.07</v>
@@ -13994,7 +13994,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR62" t="n">
         <v>1.59</v>
@@ -15302,7 +15302,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR68" t="n">
         <v>0.97</v>
@@ -16171,7 +16171,7 @@
         <v>0.33</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.43</v>
@@ -16607,7 +16607,7 @@
         <v>0.33</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.93</v>
@@ -16828,7 +16828,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR75" t="n">
         <v>2.02</v>
@@ -17261,7 +17261,7 @@
         <v>0.67</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ77" t="n">
         <v>1</v>
@@ -17482,7 +17482,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR78" t="n">
         <v>1.36</v>
@@ -18351,7 +18351,7 @@
         <v>1.33</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.43</v>
@@ -19880,7 +19880,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR89" t="n">
         <v>1.07</v>
@@ -20534,7 +20534,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR92" t="n">
         <v>2.49</v>
@@ -20749,7 +20749,7 @@
         <v>1.75</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.2</v>
@@ -21188,7 +21188,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR95" t="n">
         <v>1.99</v>
@@ -21621,7 +21621,7 @@
         <v>1</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ97" t="n">
         <v>0.57</v>
@@ -23586,7 +23586,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR106" t="n">
         <v>1.71</v>
@@ -24455,7 +24455,7 @@
         <v>1</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.43</v>
@@ -24673,7 +24673,7 @@
         <v>2</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.57</v>
@@ -26420,7 +26420,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR119" t="n">
         <v>2.56</v>
@@ -26638,7 +26638,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ120" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR120" t="n">
         <v>1.73</v>
@@ -29469,7 +29469,7 @@
         <v>0.6</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ133" t="n">
         <v>0.57</v>
@@ -29905,7 +29905,7 @@
         <v>1.67</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.2</v>
@@ -30126,7 +30126,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR136" t="n">
         <v>1.68</v>
@@ -30341,7 +30341,7 @@
         <v>1.17</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.2</v>
@@ -31216,7 +31216,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR141" t="n">
         <v>1.39</v>
@@ -31431,7 +31431,7 @@
         <v>1.6</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ142" t="n">
         <v>1.14</v>
@@ -31652,7 +31652,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR143" t="n">
         <v>1.26</v>
@@ -34268,7 +34268,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR155" t="n">
         <v>1.44</v>
@@ -34486,7 +34486,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR156" t="n">
         <v>1.56</v>
@@ -34922,7 +34922,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR158" t="n">
         <v>1.77</v>
@@ -35573,7 +35573,7 @@
         <v>1.29</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ161" t="n">
         <v>1.21</v>
@@ -35791,7 +35791,7 @@
         <v>1</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ162" t="n">
         <v>1.23</v>
@@ -36445,7 +36445,7 @@
         <v>1.5</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.14</v>
@@ -39497,7 +39497,7 @@
         <v>1.29</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ179" t="n">
         <v>1.14</v>
@@ -39715,7 +39715,7 @@
         <v>0.86</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ180" t="n">
         <v>1.23</v>
@@ -39933,7 +39933,7 @@
         <v>1.86</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ181" t="n">
         <v>1.71</v>
@@ -40590,7 +40590,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR184" t="n">
         <v>1.46</v>
@@ -41026,7 +41026,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR186" t="n">
         <v>1.2</v>
@@ -41462,7 +41462,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ188" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR188" t="n">
         <v>1.69</v>
@@ -44511,7 +44511,7 @@
         <v>2</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ202" t="n">
         <v>1.71</v>
@@ -45383,7 +45383,7 @@
         <v>0.78</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ206" t="n">
         <v>0.93</v>
@@ -45822,7 +45822,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ208" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR208" t="n">
         <v>1.21</v>
@@ -46040,7 +46040,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR209" t="n">
         <v>1.52</v>
@@ -46255,10 +46255,10 @@
         <v>1.56</v>
       </c>
       <c r="AP210" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ210" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR210" t="n">
         <v>1.36</v>
@@ -48871,7 +48871,7 @@
         <v>1.33</v>
       </c>
       <c r="AP222" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ222" t="n">
         <v>1.23</v>
@@ -49307,10 +49307,10 @@
         <v>1.3</v>
       </c>
       <c r="AP224" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ224" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR224" t="n">
         <v>1.14</v>
@@ -50182,7 +50182,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ228" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR228" t="n">
         <v>1.77</v>
@@ -50618,7 +50618,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ230" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR230" t="n">
         <v>1.56</v>
@@ -51051,7 +51051,7 @@
         <v>1.4</v>
       </c>
       <c r="AP232" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ232" t="n">
         <v>1.43</v>
@@ -53888,7 +53888,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ245" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR245" t="n">
         <v>1.86</v>
@@ -54757,7 +54757,7 @@
         <v>1</v>
       </c>
       <c r="AP249" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ249" t="n">
         <v>1</v>
@@ -55414,7 +55414,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ252" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR252" t="n">
         <v>1.27</v>
@@ -56065,7 +56065,7 @@
         <v>1.55</v>
       </c>
       <c r="AP255" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ255" t="n">
         <v>1.57</v>
@@ -56286,7 +56286,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ256" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR256" t="n">
         <v>1.58</v>
@@ -57809,7 +57809,7 @@
         <v>1.27</v>
       </c>
       <c r="AP263" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ263" t="n">
         <v>1.07</v>
@@ -59338,7 +59338,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ270" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR270" t="n">
         <v>1.76</v>
@@ -59553,7 +59553,7 @@
         <v>1.33</v>
       </c>
       <c r="AP271" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ271" t="n">
         <v>1.43</v>
@@ -59774,7 +59774,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ272" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR272" t="n">
         <v>1.46</v>
@@ -61300,7 +61300,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ279" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR279" t="n">
         <v>1.3</v>
@@ -62169,7 +62169,7 @@
         <v>0.83</v>
       </c>
       <c r="AP283" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ283" t="n">
         <v>0.93</v>
@@ -62823,7 +62823,7 @@
         <v>1.08</v>
       </c>
       <c r="AP286" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ286" t="n">
         <v>1.14</v>
@@ -63477,7 +63477,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP289" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ289" t="n">
         <v>0.86</v>
@@ -64134,7 +64134,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ292" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR292" t="n">
         <v>1.44</v>
@@ -64570,7 +64570,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ294" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR294" t="n">
         <v>1.63</v>
@@ -65006,7 +65006,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ296" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR296" t="n">
         <v>1.76</v>
@@ -65221,7 +65221,7 @@
         <v>0.62</v>
       </c>
       <c r="AP297" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ297" t="n">
         <v>0.79</v>
@@ -66747,7 +66747,7 @@
         <v>1.71</v>
       </c>
       <c r="AP304" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ304" t="n">
         <v>1.8</v>
@@ -67916,6 +67916,660 @@
       </c>
       <c r="BP309" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" t="n">
+        <v>8235212</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="n">
+        <v>46087.6875</v>
+      </c>
+      <c r="F310" t="n">
+        <v>29</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Real Zaragoza</t>
+        </is>
+      </c>
+      <c r="I310" t="n">
+        <v>0</v>
+      </c>
+      <c r="J310" t="n">
+        <v>1</v>
+      </c>
+      <c r="K310" t="n">
+        <v>1</v>
+      </c>
+      <c r="L310" t="n">
+        <v>0</v>
+      </c>
+      <c r="M310" t="n">
+        <v>1</v>
+      </c>
+      <c r="N310" t="n">
+        <v>1</v>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="Q310" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R310" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S310" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T310" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U310" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V310" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W310" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X310" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y310" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z310" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA310" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB310" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC310" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD310" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE310" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF310" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AG310" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AH310" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI310" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ310" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK310" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM310" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN310" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO310" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AP310" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ310" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR310" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS310" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT310" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU310" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV310" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW310" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX310" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY310" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ310" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA310" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB310" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC310" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD310" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE310" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF310" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG310" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH310" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI310" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BJ310" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BK310" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BL310" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM310" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN310" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BO310" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP310" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" t="n">
+        <v>8235080</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="n">
+        <v>46088.51041666666</v>
+      </c>
+      <c r="F311" t="n">
+        <v>29</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>SD Huesca</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Albacete Balompié</t>
+        </is>
+      </c>
+      <c r="I311" t="n">
+        <v>0</v>
+      </c>
+      <c r="J311" t="n">
+        <v>0</v>
+      </c>
+      <c r="K311" t="n">
+        <v>0</v>
+      </c>
+      <c r="L311" t="n">
+        <v>0</v>
+      </c>
+      <c r="M311" t="n">
+        <v>0</v>
+      </c>
+      <c r="N311" t="n">
+        <v>0</v>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q311" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="R311" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S311" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="T311" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U311" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V311" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W311" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X311" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y311" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z311" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA311" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AB311" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC311" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD311" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AE311" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF311" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AG311" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH311" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI311" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ311" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK311" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM311" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN311" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO311" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AP311" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ311" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR311" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS311" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT311" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AU311" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV311" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW311" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX311" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY311" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ311" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA311" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB311" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC311" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD311" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BE311" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF311" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BG311" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH311" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI311" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ311" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BK311" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BL311" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM311" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BN311" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO311" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP311" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" t="n">
+        <v>8235079</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="n">
+        <v>46088.51041666666</v>
+      </c>
+      <c r="F312" t="n">
+        <v>29</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Real Sociedad II</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>CD Castellón</t>
+        </is>
+      </c>
+      <c r="I312" t="n">
+        <v>2</v>
+      </c>
+      <c r="J312" t="n">
+        <v>2</v>
+      </c>
+      <c r="K312" t="n">
+        <v>4</v>
+      </c>
+      <c r="L312" t="n">
+        <v>4</v>
+      </c>
+      <c r="M312" t="n">
+        <v>2</v>
+      </c>
+      <c r="N312" t="n">
+        <v>6</v>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>['2', '6', '69', '90+3']</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>['5', '24']</t>
+        </is>
+      </c>
+      <c r="Q312" t="n">
+        <v>4</v>
+      </c>
+      <c r="R312" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S312" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T312" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U312" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V312" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="W312" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X312" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y312" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z312" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA312" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB312" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC312" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD312" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE312" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF312" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AG312" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH312" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI312" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ312" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK312" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL312" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM312" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN312" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO312" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP312" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ312" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR312" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AS312" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AT312" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU312" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV312" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW312" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX312" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY312" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ312" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA312" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB312" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC312" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD312" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE312" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF312" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BG312" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH312" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI312" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ312" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BK312" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BL312" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BM312" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BN312" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO312" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP312" t="n">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Spain Segunda División_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Spain Segunda División_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP312"/>
+  <dimension ref="A1:BP314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.21</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.38</v>
@@ -2222,7 +2222,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.79</v>
@@ -7454,7 +7454,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR32" t="n">
         <v>1.33</v>
@@ -8108,7 +8108,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR35" t="n">
         <v>0.92</v>
@@ -8762,7 +8762,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR38" t="n">
         <v>1.68</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ39" t="n">
         <v>1</v>
@@ -9631,7 +9631,7 @@
         <v>3</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.57</v>
@@ -13558,7 +13558,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR60" t="n">
         <v>1.58</v>
@@ -14212,7 +14212,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR63" t="n">
         <v>1.48</v>
@@ -14645,7 +14645,7 @@
         <v>1</v>
       </c>
       <c r="AP65" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.07</v>
@@ -15081,7 +15081,7 @@
         <v>0.5</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ67" t="n">
         <v>1</v>
@@ -16389,7 +16389,7 @@
         <v>1.5</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.14</v>
@@ -19444,7 +19444,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR87" t="n">
         <v>1.75</v>
@@ -21839,10 +21839,10 @@
         <v>1.33</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR98" t="n">
         <v>1.3</v>
@@ -22057,7 +22057,7 @@
         <v>2</v>
       </c>
       <c r="AP99" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.8</v>
@@ -22714,7 +22714,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR102" t="n">
         <v>1.44</v>
@@ -25763,7 +25763,7 @@
         <v>0</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.79</v>
@@ -26199,7 +26199,7 @@
         <v>1.4</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.2</v>
@@ -26856,7 +26856,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR121" t="n">
         <v>1.5</v>
@@ -27292,7 +27292,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR123" t="n">
         <v>1.11</v>
@@ -30777,7 +30777,7 @@
         <v>1.33</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.43</v>
@@ -31434,7 +31434,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR142" t="n">
         <v>1.3</v>
@@ -31649,7 +31649,7 @@
         <v>1.17</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.33</v>
@@ -36009,7 +36009,7 @@
         <v>1.67</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.71</v>
@@ -36227,10 +36227,10 @@
         <v>1.14</v>
       </c>
       <c r="AP164" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ164" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR164" t="n">
         <v>1.62</v>
@@ -36448,7 +36448,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR165" t="n">
         <v>1.15</v>
@@ -39500,7 +39500,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR179" t="n">
         <v>1.34</v>
@@ -41023,7 +41023,7 @@
         <v>1.13</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ186" t="n">
         <v>1.2</v>
@@ -41244,7 +41244,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ187" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR187" t="n">
         <v>1.39</v>
@@ -41459,7 +41459,7 @@
         <v>0.88</v>
       </c>
       <c r="AP188" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ188" t="n">
         <v>1.07</v>
@@ -43860,7 +43860,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ199" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR199" t="n">
         <v>1.92</v>
@@ -44078,7 +44078,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR200" t="n">
         <v>1.92</v>
@@ -45165,7 +45165,7 @@
         <v>1.67</v>
       </c>
       <c r="AP205" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ205" t="n">
         <v>1.43</v>
@@ -45819,7 +45819,7 @@
         <v>0.89</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ208" t="n">
         <v>1.07</v>
@@ -46476,7 +46476,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ211" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR211" t="n">
         <v>1.86</v>
@@ -49743,7 +49743,7 @@
         <v>0.33</v>
       </c>
       <c r="AP226" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ226" t="n">
         <v>0.38</v>
@@ -50400,7 +50400,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ229" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR229" t="n">
         <v>1.41</v>
@@ -50833,7 +50833,7 @@
         <v>1</v>
       </c>
       <c r="AP231" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ231" t="n">
         <v>0.93</v>
@@ -51490,7 +51490,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ234" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR234" t="n">
         <v>1.43</v>
@@ -52795,7 +52795,7 @@
         <v>0.7</v>
       </c>
       <c r="AP240" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ240" t="n">
         <v>0.57</v>
@@ -53667,7 +53667,7 @@
         <v>1.6</v>
       </c>
       <c r="AP244" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ244" t="n">
         <v>1.43</v>
@@ -54324,7 +54324,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ247" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR247" t="n">
         <v>1.6</v>
@@ -56501,7 +56501,7 @@
         <v>1.42</v>
       </c>
       <c r="AP257" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ257" t="n">
         <v>1.2</v>
@@ -56940,7 +56940,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ259" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR259" t="n">
         <v>1.79</v>
@@ -60207,7 +60207,7 @@
         <v>1.33</v>
       </c>
       <c r="AP274" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ274" t="n">
         <v>1.21</v>
@@ -60428,7 +60428,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ275" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR275" t="n">
         <v>1.84</v>
@@ -61079,7 +61079,7 @@
         <v>1.17</v>
       </c>
       <c r="AP278" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ278" t="n">
         <v>1.07</v>
@@ -61518,7 +61518,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ280" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR280" t="n">
         <v>1.54</v>
@@ -63480,7 +63480,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ289" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR289" t="n">
         <v>1.36</v>
@@ -64352,7 +64352,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ293" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR293" t="n">
         <v>1.61</v>
@@ -65003,7 +65003,7 @@
         <v>1.31</v>
       </c>
       <c r="AP296" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ296" t="n">
         <v>1.2</v>
@@ -68309,10 +68309,10 @@
         <v>5</v>
       </c>
       <c r="BB311" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC311" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD311" t="n">
         <v>1.82</v>
@@ -68570,6 +68570,442 @@
       </c>
       <c r="BP312" t="n">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" t="n">
+        <v>8235071</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="n">
+        <v>46088.60416666666</v>
+      </c>
+      <c r="F313" t="n">
+        <v>29</v>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Burgos CF</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Mirandés</t>
+        </is>
+      </c>
+      <c r="I313" t="n">
+        <v>1</v>
+      </c>
+      <c r="J313" t="n">
+        <v>0</v>
+      </c>
+      <c r="K313" t="n">
+        <v>1</v>
+      </c>
+      <c r="L313" t="n">
+        <v>2</v>
+      </c>
+      <c r="M313" t="n">
+        <v>0</v>
+      </c>
+      <c r="N313" t="n">
+        <v>2</v>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>['21', '66']</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q313" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R313" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S313" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="T313" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U313" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V313" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="W313" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X313" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y313" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z313" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA313" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB313" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC313" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD313" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AE313" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF313" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AG313" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AH313" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI313" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AJ313" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AK313" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AL313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM313" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN313" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO313" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP313" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ313" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR313" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AS313" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AT313" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AU313" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV313" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW313" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX313" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY313" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ313" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA313" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB313" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC313" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD313" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE313" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF313" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG313" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BH313" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BI313" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BJ313" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BK313" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL313" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BM313" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BN313" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BO313" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP313" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" t="n">
+        <v>8235158</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="n">
+        <v>46088.70833333334</v>
+      </c>
+      <c r="F314" t="n">
+        <v>29</v>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Málaga CF</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Real Valladolid</t>
+        </is>
+      </c>
+      <c r="I314" t="n">
+        <v>2</v>
+      </c>
+      <c r="J314" t="n">
+        <v>1</v>
+      </c>
+      <c r="K314" t="n">
+        <v>3</v>
+      </c>
+      <c r="L314" t="n">
+        <v>3</v>
+      </c>
+      <c r="M314" t="n">
+        <v>3</v>
+      </c>
+      <c r="N314" t="n">
+        <v>6</v>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>['11', '14', '48']</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>['45+6', '65', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q314" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R314" t="n">
+        <v>2</v>
+      </c>
+      <c r="S314" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T314" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U314" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V314" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W314" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X314" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Y314" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z314" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA314" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB314" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AC314" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD314" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AE314" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF314" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AG314" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH314" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI314" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ314" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK314" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM314" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN314" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AO314" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP314" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ314" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR314" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS314" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT314" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU314" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV314" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW314" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX314" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY314" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ314" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA314" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB314" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC314" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD314" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BE314" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF314" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG314" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH314" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI314" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BJ314" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BK314" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BL314" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BM314" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BN314" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO314" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP314" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>
